--- a/BOM_LignePassionIIm.xlsx
+++ b/BOM_LignePassionIIm.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7a43dc3239fed0de/PCB_Perso/PCB_IIm_Ligne/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/79fc430203973324/TravauxMetriques/IIm/Passion IIm/PupitreLigne/AlimLigne_PassionIIm/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="232" documentId="8_{D99A6803-265B-43E3-9609-960129D8CCE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7E70655-7E73-4000-81D6-90B5998025DA}"/>
+  <xr:revisionPtr revIDLastSave="325" documentId="8_{D99A6803-265B-43E3-9609-960129D8CCE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{554F8893-E192-42BB-B486-75A96D8534B9}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{C3AD9156-7CE6-4A1E-A3FD-D08ECF380023}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{C3AD9156-7CE6-4A1E-A3FD-D08ECF380023}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="96">
   <si>
     <t>Quoi</t>
   </si>
@@ -198,9 +198,6 @@
     <t>Mosfet</t>
   </si>
   <si>
-    <t>Q5</t>
-  </si>
-  <si>
     <t>IRF4905PBF</t>
   </si>
   <si>
@@ -240,9 +237,6 @@
     <t>D1, D2, D3, D4</t>
   </si>
   <si>
-    <t>J1, J2</t>
-  </si>
-  <si>
     <t>AliExpress</t>
   </si>
   <si>
@@ -291,7 +285,67 @@
     <t>10K</t>
   </si>
   <si>
-    <t>1K</t>
+    <t>Q6</t>
+  </si>
+  <si>
+    <t>Interrupteur</t>
+  </si>
+  <si>
+    <t>Bouton poussoir</t>
+  </si>
+  <si>
+    <t>Led</t>
+  </si>
+  <si>
+    <t>vertes</t>
+  </si>
+  <si>
+    <t>jaunes</t>
+  </si>
+  <si>
+    <t>3 pos 3 cont</t>
+  </si>
+  <si>
+    <t>J1, J2, (J3)</t>
+  </si>
+  <si>
+    <t>R1, R2, R5, R6</t>
+  </si>
+  <si>
+    <t>Pour led</t>
+  </si>
+  <si>
+    <t>R4</t>
+  </si>
+  <si>
+    <t>R7</t>
+  </si>
+  <si>
+    <t>R9, R18</t>
+  </si>
+  <si>
+    <t>R8, R10, R13, R14, R19</t>
+  </si>
+  <si>
+    <t>270R 1/4W</t>
+  </si>
+  <si>
+    <t>Resistance (À changer)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">470R </t>
+  </si>
+  <si>
+    <t>R12, R15</t>
+  </si>
+  <si>
+    <t>1K 1/4W</t>
+  </si>
+  <si>
+    <t>Capuchon pour pot</t>
+  </si>
+  <si>
+    <t>~1000uF</t>
   </si>
 </sst>
 </file>
@@ -554,11 +608,12 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color auto="1"/>
+        <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;CHF&quot;_-;\-* #,##0.00\ &quot;CHF&quot;_-;_-* &quot;-&quot;??\ &quot;CHF&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
       <font>
@@ -572,7 +627,7 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color theme="1"/>
+        <color auto="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -684,8 +739,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{69225E41-4DDD-470A-8E1A-242AA800D3ED}" name="Tableau2" displayName="Tableau2" ref="A2:L25" totalsRowShown="0" headerRowDxfId="4" headerRowBorderDxfId="3">
-  <autoFilter ref="A2:L25" xr:uid="{69225E41-4DDD-470A-8E1A-242AA800D3ED}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{69225E41-4DDD-470A-8E1A-242AA800D3ED}" name="Tableau2" displayName="Tableau2" ref="A2:L32" totalsRowShown="0" headerRowDxfId="4" headerRowBorderDxfId="3">
+  <autoFilter ref="A2:L32" xr:uid="{69225E41-4DDD-470A-8E1A-242AA800D3ED}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{4A89CEB1-B61F-4362-A305-55FE015108C9}" name="Quoi"/>
     <tableColumn id="12" xr3:uid="{DA7C8F96-35E1-4693-8B7A-073C30B6A014}" name="Variante"/>
@@ -695,8 +750,10 @@
     <tableColumn id="5" xr3:uid="{99AE4783-A1AE-4A59-8D0A-2F21D4650621}" name="Qty/PCB"/>
     <tableColumn id="6" xr3:uid="{7DFEF622-3863-4E1B-9C42-44C137F57007}" name="Qty/Tot"/>
     <tableColumn id="7" xr3:uid="{395CF200-6735-4436-81FB-32A22C5D952F}" name="Prix" dataDxfId="2" dataCellStyle="Monétaire"/>
-    <tableColumn id="8" xr3:uid="{AF9D19B1-93B1-4ACE-B10F-818FD3288CA4}" name="PrixTot/PCB" dataDxfId="1" dataCellStyle="Monétaire"/>
-    <tableColumn id="9" xr3:uid="{B4254C8A-C5D7-4572-B86E-606DB6474104}" name="Fabriquant" dataDxfId="0"/>
+    <tableColumn id="8" xr3:uid="{AF9D19B1-93B1-4ACE-B10F-818FD3288CA4}" name="PrixTot/PCB" dataDxfId="0" dataCellStyle="Monétaire">
+      <calculatedColumnFormula>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{B4254C8A-C5D7-4572-B86E-606DB6474104}" name="Fabriquant" dataDxfId="1"/>
     <tableColumn id="10" xr3:uid="{CF25DBB4-03E2-4519-889D-8135C83E9E6E}" name="Fournisseur "/>
     <tableColumn id="11" xr3:uid="{BD2CA350-D119-422A-BE3F-FA523F34F5B9}" name="Lien "/>
   </tableColumns>
@@ -1021,21 +1078,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3B7EC6F-57FE-4577-A1D4-89717E48955F}">
-  <dimension ref="A1:L33"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:L40"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.59765625" customWidth="1"/>
-    <col min="2" max="2" width="18.1328125" customWidth="1"/>
-    <col min="3" max="3" width="12.796875" customWidth="1"/>
-    <col min="4" max="4" width="12.73046875" customWidth="1"/>
-    <col min="5" max="5" width="16.86328125" customWidth="1"/>
-    <col min="9" max="9" width="12.1328125" customWidth="1"/>
-    <col min="10" max="10" width="19.86328125" customWidth="1"/>
-    <col min="11" max="11" width="12.3984375" customWidth="1"/>
-    <col min="12" max="12" width="79.53125" customWidth="1"/>
+    <col min="1" max="1" width="25.5546875" customWidth="1"/>
+    <col min="2" max="2" width="18.109375" customWidth="1"/>
+    <col min="3" max="3" width="12.77734375" customWidth="1"/>
+    <col min="4" max="4" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.88671875" customWidth="1"/>
+    <col min="9" max="9" width="12.109375" customWidth="1"/>
+    <col min="10" max="10" width="19.88671875" customWidth="1"/>
+    <col min="11" max="11" width="12.44140625" customWidth="1"/>
+    <col min="12" max="12" width="79.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
         <v>31</v>
       </c>
@@ -1051,7 +1108,7 @@
       <c r="K1" s="14"/>
       <c r="L1" s="14"/>
     </row>
-    <row r="2" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="12" t="s">
         <v>0</v>
       </c>
@@ -1089,7 +1146,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1105,7 +1162,10 @@
       <c r="H3" s="2">
         <v>8.7200000000000006</v>
       </c>
-      <c r="I3" s="2"/>
+      <c r="I3" s="2">
+        <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
+        <v>8.7200000000000006</v>
+      </c>
       <c r="J3" t="s">
         <v>10</v>
       </c>
@@ -1116,7 +1176,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -1126,13 +1186,18 @@
       <c r="F4">
         <v>1</v>
       </c>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
+      <c r="H4" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="I4" s="2">
+        <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
+        <v>0.5</v>
+      </c>
       <c r="K4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>555</v>
       </c>
@@ -1148,7 +1213,10 @@
       <c r="H5" s="2">
         <v>0.68</v>
       </c>
-      <c r="I5" s="2"/>
+      <c r="I5" s="2">
+        <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
+        <v>0.68</v>
+      </c>
       <c r="J5" t="s">
         <v>20</v>
       </c>
@@ -1159,7 +1227,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>41</v>
       </c>
@@ -1175,7 +1243,10 @@
       <c r="H6" s="2">
         <v>0.11</v>
       </c>
-      <c r="I6" s="2"/>
+      <c r="I6" s="2">
+        <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
+        <v>0.11</v>
+      </c>
       <c r="J6" s="4" t="s">
         <v>21</v>
       </c>
@@ -1186,7 +1257,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>41</v>
       </c>
@@ -1203,7 +1274,10 @@
       <c r="H7" s="2">
         <v>8.5000000000000006E-2</v>
       </c>
-      <c r="I7" s="2"/>
+      <c r="I7" s="2">
+        <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
+        <v>0.255</v>
+      </c>
       <c r="J7" s="4" t="s">
         <v>21</v>
       </c>
@@ -1214,15 +1288,15 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>45</v>
       </c>
       <c r="C8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E8" t="s">
         <v>46</v>
-      </c>
-      <c r="E8" t="s">
-        <v>47</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -1230,100 +1304,116 @@
       <c r="H8" s="2">
         <v>2.48</v>
       </c>
-      <c r="I8" s="2"/>
+      <c r="I8" s="2">
+        <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
+        <v>2.48</v>
+      </c>
       <c r="J8" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K8" t="s">
         <v>11</v>
       </c>
       <c r="L8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>49</v>
+      </c>
+      <c r="D9" t="s">
+        <v>95</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
+      <c r="I9" s="2">
+        <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
+        <v>0</v>
+      </c>
       <c r="J9" s="4"/>
-      <c r="K9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>24</v>
       </c>
       <c r="C10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" t="s">
         <v>52</v>
-      </c>
-      <c r="D10" t="s">
-        <v>53</v>
       </c>
       <c r="F10">
         <v>1</v>
       </c>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
+      <c r="H10" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="I10" s="2">
+        <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
+        <v>0.05</v>
+      </c>
       <c r="J10" s="4"/>
       <c r="K10" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>24</v>
       </c>
       <c r="C11" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11" t="s">
         <v>54</v>
-      </c>
-      <c r="D11" t="s">
-        <v>55</v>
       </c>
       <c r="F11">
         <v>1</v>
       </c>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
+      <c r="H11" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="I11" s="2">
+        <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
+        <v>0.05</v>
+      </c>
       <c r="J11" s="4"/>
       <c r="K11" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>24</v>
       </c>
       <c r="C12" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" t="s">
         <v>56</v>
-      </c>
-      <c r="D12" t="s">
-        <v>57</v>
       </c>
       <c r="F12">
         <v>1</v>
       </c>
       <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
+      <c r="I12" s="2">
+        <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
+        <v>0</v>
+      </c>
       <c r="J12" s="4"/>
-      <c r="K12" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>57</v>
+      </c>
+      <c r="C13" t="s">
         <v>58</v>
-      </c>
-      <c r="C13" t="s">
-        <v>59</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" t="s">
@@ -1335,7 +1425,10 @@
       <c r="H13" s="2">
         <v>6.8000000000000005E-2</v>
       </c>
-      <c r="I13" s="2"/>
+      <c r="I13" s="2">
+        <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
+        <v>0.27200000000000002</v>
+      </c>
       <c r="J13" s="4" t="s">
         <v>21</v>
       </c>
@@ -1346,148 +1439,222 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C14" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="D14" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
+      <c r="I14" s="2">
+        <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
+        <v>0</v>
+      </c>
       <c r="J14" s="4"/>
       <c r="K14" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C15" t="s">
         <v>28</v>
       </c>
       <c r="D15" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F15">
         <v>1</v>
       </c>
       <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
+      <c r="I15" s="2">
+        <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
+        <v>0</v>
+      </c>
       <c r="K15" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>27</v>
       </c>
+      <c r="C16" t="s">
+        <v>88</v>
+      </c>
       <c r="D16" t="s">
-        <v>76</v>
-      </c>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="F16">
+        <v>5</v>
+      </c>
+      <c r="H16" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="I16" s="2">
+        <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
+        <v>0.25</v>
+      </c>
       <c r="J16" s="4"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="K16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>27</v>
       </c>
+      <c r="C17" t="s">
+        <v>92</v>
+      </c>
       <c r="D17" t="s">
-        <v>77</v>
-      </c>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
+        <v>93</v>
+      </c>
+      <c r="F17">
+        <v>2</v>
+      </c>
+      <c r="H17" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="I17" s="2">
+        <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
+        <v>0.1</v>
+      </c>
       <c r="J17" s="4"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="K17" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="3">
-        <v>200</v>
-      </c>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
+      <c r="C18" t="s">
+        <v>86</v>
+      </c>
+      <c r="D18" t="s">
+        <v>91</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="H18" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="I18" s="2">
+        <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
+        <v>0.05</v>
+      </c>
       <c r="J18" s="4"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="K18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>27</v>
       </c>
-      <c r="D19" s="3">
-        <v>260</v>
-      </c>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="C19" t="s">
+        <v>87</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F19">
+        <v>2</v>
+      </c>
+      <c r="H19" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="I19" s="2">
+        <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
+        <v>0.1</v>
+      </c>
+      <c r="J19" s="4"/>
+      <c r="K19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>65</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="C20" t="s">
+        <v>85</v>
+      </c>
+      <c r="D20" s="3"/>
       <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="H20" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="I20" s="2">
+        <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
+        <v>0.05</v>
+      </c>
+      <c r="K20" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" t="s">
+        <v>83</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F21">
+        <v>4</v>
+      </c>
+      <c r="H21" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="I21" s="2">
+        <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
+        <v>0.2</v>
+      </c>
+      <c r="K21" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>63</v>
+      </c>
+      <c r="F22">
         <v>2</v>
       </c>
-      <c r="H20" s="2">
+      <c r="H22" s="2">
         <v>2.4500000000000002</v>
       </c>
-      <c r="I20" s="2"/>
-      <c r="J20" s="4"/>
-      <c r="K20" t="s">
-        <v>73</v>
-      </c>
-      <c r="L20" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A21" t="s">
-        <v>67</v>
-      </c>
-      <c r="F21">
-        <v>1</v>
-      </c>
-      <c r="H21" s="2">
-        <v>5.1999999999999998E-2</v>
-      </c>
-      <c r="I21" s="2"/>
-      <c r="J21" s="4"/>
-      <c r="K21" t="s">
-        <v>61</v>
-      </c>
-      <c r="L21" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A22" t="s">
-        <v>68</v>
-      </c>
-      <c r="F22">
-        <v>1</v>
-      </c>
-      <c r="H22" s="2">
-        <v>5.1999999999999998E-2</v>
-      </c>
-      <c r="I22" s="2"/>
+      <c r="I22" s="2">
+        <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
+        <v>4.9000000000000004</v>
+      </c>
       <c r="J22" s="4"/>
       <c r="K22" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="L22" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.45">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="F23">
         <v>1</v>
@@ -1495,130 +1662,278 @@
       <c r="H23" s="2">
         <v>5.1999999999999998E-2</v>
       </c>
-      <c r="I23" s="2"/>
+      <c r="I23" s="2">
+        <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
+        <v>5.1999999999999998E-2</v>
+      </c>
       <c r="J23" s="4"/>
       <c r="K23" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="L23" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.45">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H24" s="2">
         <v>5.1999999999999998E-2</v>
       </c>
-      <c r="I24" s="2"/>
+      <c r="I24" s="2">
+        <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
+        <v>5.1999999999999998E-2</v>
+      </c>
       <c r="J24" s="4"/>
       <c r="K24" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="L24" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.45">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>66</v>
-      </c>
-      <c r="D25" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F25">
         <v>1</v>
       </c>
       <c r="H25" s="2">
-        <v>4.25</v>
-      </c>
-      <c r="I25" s="2"/>
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="I25" s="2">
+        <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
+        <v>5.1999999999999998E-2</v>
+      </c>
       <c r="J25" s="4"/>
       <c r="K25" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="L25" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>67</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="H26" s="2">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="I26" s="2">
+        <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="J26" s="4"/>
+      <c r="K26" t="s">
+        <v>59</v>
+      </c>
+      <c r="L26" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>64</v>
+      </c>
+      <c r="D27" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A27" s="6" t="s">
+      <c r="F27">
+        <v>1</v>
+      </c>
+      <c r="H27" s="2">
+        <v>4.25</v>
+      </c>
+      <c r="I27" s="2">
+        <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
+        <v>4.25</v>
+      </c>
+      <c r="J27" s="4"/>
+      <c r="K27" t="s">
+        <v>71</v>
+      </c>
+      <c r="L27" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>94</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2">
+        <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
+        <v>0</v>
+      </c>
+      <c r="J28" s="4"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>76</v>
+      </c>
+      <c r="D29" t="s">
+        <v>81</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2">
+        <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
+        <v>0</v>
+      </c>
+      <c r="J29" s="4"/>
+      <c r="K29" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>77</v>
+      </c>
+      <c r="F30">
+        <v>2</v>
+      </c>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2">
+        <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
+        <v>0</v>
+      </c>
+      <c r="J30" s="4"/>
+      <c r="K30" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>78</v>
+      </c>
+      <c r="D31" t="s">
+        <v>79</v>
+      </c>
+      <c r="F31">
+        <v>2</v>
+      </c>
+      <c r="H31" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="I31" s="2">
+        <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
+        <v>0.1</v>
+      </c>
+      <c r="J31" s="4"/>
+      <c r="K31" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>78</v>
+      </c>
+      <c r="D32" t="s">
+        <v>80</v>
+      </c>
+      <c r="F32">
+        <v>2</v>
+      </c>
+      <c r="H32" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="I32" s="2">
+        <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
+        <v>0.1</v>
+      </c>
+      <c r="J32" s="4"/>
+      <c r="K32" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A34" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="8">
+      <c r="B34" s="6"/>
+      <c r="C34" s="8">
         <v>46126</v>
       </c>
-      <c r="D27" s="15" t="e" vm="1">
+      <c r="D34" s="15" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="E27" s="16"/>
-      <c r="F27" s="17"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A28" s="7" t="s">
+      <c r="E34" s="16"/>
+      <c r="F34" s="17"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A35" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B28" s="7"/>
-      <c r="C28" s="9" t="s">
+      <c r="B35" s="7"/>
+      <c r="C35" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D28" s="18"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="19"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A29" s="7" t="s">
+      <c r="D35" s="18"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="19"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A36" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B29" s="7"/>
-      <c r="C29" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="D29" s="18"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="19"/>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A30" s="10" t="s">
+      <c r="B36" s="7"/>
+      <c r="C36" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D36" s="18"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="19"/>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A37" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="B30" s="10"/>
-      <c r="C30" s="11" t="s">
+      <c r="B37" s="10"/>
+      <c r="C37" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="D30" s="20"/>
-      <c r="E30" s="21"/>
-      <c r="F30" s="22"/>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A31" s="1"/>
-      <c r="B31" s="1"/>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A32" s="1"/>
-      <c r="B32" s="1"/>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A33" s="1"/>
-      <c r="B33" s="1"/>
+      <c r="D37" s="20"/>
+      <c r="E37" s="21"/>
+      <c r="F37" s="22"/>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A38" s="1"/>
+      <c r="B38" s="1"/>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A39" s="1"/>
+      <c r="B39" s="1"/>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A40" s="1"/>
+      <c r="B40" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:L1"/>
-    <mergeCell ref="D27:F30"/>
+    <mergeCell ref="D34:F37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/BOM_LignePassionIIm.xlsx
+++ b/BOM_LignePassionIIm.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/79fc430203973324/TravauxMetriques/IIm/Passion IIm/PupitreLigne/AlimLigne_PassionIIm/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7a43dc3239fed0de/PCB_Perso/PCB_IIm_Ligne/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="325" documentId="8_{D99A6803-265B-43E3-9609-960129D8CCE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{554F8893-E192-42BB-B486-75A96D8534B9}"/>
+  <xr:revisionPtr revIDLastSave="348" documentId="8_{D99A6803-265B-43E3-9609-960129D8CCE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8FC5694C-C4FF-4997-9199-556382D8D3CF}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{C3AD9156-7CE6-4A1E-A3FD-D08ECF380023}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{C3AD9156-7CE6-4A1E-A3FD-D08ECF380023}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="99">
   <si>
     <t>Quoi</t>
   </si>
@@ -90,21 +90,12 @@
     <t>Relai BiStable de Puissance</t>
   </si>
   <si>
-    <t>Omron</t>
-  </si>
-  <si>
     <t>Digikey</t>
   </si>
   <si>
-    <t>https://www.digikey.ch/fr/products/detail/omron-electronics-inc-emc-div/G2RK-2-DC12/259703</t>
-  </si>
-  <si>
     <t>Relai Bistable de Signal</t>
   </si>
   <si>
-    <t>MPSA56</t>
-  </si>
-  <si>
     <t>Ref PCB</t>
   </si>
   <si>
@@ -150,9 +141,6 @@
     <t>https://www.digikey.ch/fr/products/detail/diotec-semiconductor/1N4007/18833652</t>
   </si>
   <si>
-    <t>https://www.digikey.ch/fr/products/detail/diotec-semiconductor/MPSA56/22193185</t>
-  </si>
-  <si>
     <t>BOM - PCB Bloc de Ligne Passion IIM</t>
   </si>
   <si>
@@ -346,6 +334,27 @@
   </si>
   <si>
     <t>~1000uF</t>
+  </si>
+  <si>
+    <t>Finder</t>
+  </si>
+  <si>
+    <t>https://www.conrad.ch/fr/p/finder-41-52-6-012-4016-relais-pour-circuits-imprimes-12-v-dc-8-a-2-inverseurs-rt-1-pc-s-1419696.html</t>
+  </si>
+  <si>
+    <t>Impression 3D</t>
+  </si>
+  <si>
+    <t>https://de.aliexpress.com/item/1005012410174447.html?spm=a2g0o.productlist.main.3.1c57pPLrpPLrXF&amp;algo_pvid=8d846d87-e1c7-4911-9404-42bf57029f2f&amp;pdp_ext_f=%7B%22order%22%3A%223%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005012410174447%7C_p_origin_prod%3A</t>
+  </si>
+  <si>
+    <t>https://de.aliexpress.com/item/1005008777027854.html?spm=a2g0o.productlist.main.3.34a9f054Jnh2d5&amp;algo_pvid=a3217470-cd61-4707-8b2f-7d76497918d0&amp;pdp_ext_f=%7B%22order%22%3A%221295%22%2C%22spu_best_type%22%3A%22price%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005008777027854%7C_p_origin_prod%3A</t>
+  </si>
+  <si>
+    <t>IRFU5305PBF</t>
+  </si>
+  <si>
+    <t>https://www.conrad.ch/fr/p/infineon-technologies-irfu5305pbf-mosfet-1-canal-p-110-w-i-pak-162729.html?insert=UP</t>
   </si>
 </sst>
 </file>
@@ -355,7 +364,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;CHF&quot;_-;\-* #,##0.00\ &quot;CHF&quot;_-;_-* &quot;-&quot;??\ &quot;CHF&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -382,6 +391,14 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -526,11 +543,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -563,6 +581,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -590,12 +609,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Lien hypertexte" xfId="2" builtinId="8"/>
     <cellStyle name="Monétaire" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="5">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -614,24 +653,6 @@
         <scheme val="minor"/>
       </font>
       <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;CHF&quot;_-;\-* #,##0.00\ &quot;CHF&quot;_-;_-* &quot;-&quot;??\ &quot;CHF&quot;_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -750,10 +771,10 @@
     <tableColumn id="5" xr3:uid="{99AE4783-A1AE-4A59-8D0A-2F21D4650621}" name="Qty/PCB"/>
     <tableColumn id="6" xr3:uid="{7DFEF622-3863-4E1B-9C42-44C137F57007}" name="Qty/Tot"/>
     <tableColumn id="7" xr3:uid="{395CF200-6735-4436-81FB-32A22C5D952F}" name="Prix" dataDxfId="2" dataCellStyle="Monétaire"/>
-    <tableColumn id="8" xr3:uid="{AF9D19B1-93B1-4ACE-B10F-818FD3288CA4}" name="PrixTot/PCB" dataDxfId="0" dataCellStyle="Monétaire">
+    <tableColumn id="8" xr3:uid="{AF9D19B1-93B1-4ACE-B10F-818FD3288CA4}" name="PrixTot/PCB" dataDxfId="1" dataCellStyle="Monétaire">
       <calculatedColumnFormula>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{B4254C8A-C5D7-4572-B86E-606DB6474104}" name="Fabriquant" dataDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{B4254C8A-C5D7-4572-B86E-606DB6474104}" name="Fabriquant" dataDxfId="0"/>
     <tableColumn id="10" xr3:uid="{CF25DBB4-03E2-4519-889D-8135C83E9E6E}" name="Fournisseur "/>
     <tableColumn id="11" xr3:uid="{BD2CA350-D119-422A-BE3F-FA523F34F5B9}" name="Lien "/>
   </tableColumns>
@@ -1079,47 +1100,47 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3B7EC6F-57FE-4577-A1D4-89717E48955F}">
   <dimension ref="A1:L40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="25.5546875" customWidth="1"/>
-    <col min="2" max="2" width="18.109375" customWidth="1"/>
-    <col min="3" max="3" width="12.77734375" customWidth="1"/>
-    <col min="4" max="4" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.88671875" customWidth="1"/>
-    <col min="9" max="9" width="12.109375" customWidth="1"/>
-    <col min="10" max="10" width="19.88671875" customWidth="1"/>
-    <col min="11" max="11" width="12.44140625" customWidth="1"/>
-    <col min="12" max="12" width="79.5546875" customWidth="1"/>
+    <col min="1" max="1" width="25.53125" customWidth="1"/>
+    <col min="2" max="2" width="18.1328125" customWidth="1"/>
+    <col min="3" max="3" width="12.796875" customWidth="1"/>
+    <col min="4" max="4" width="14.1328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.86328125" customWidth="1"/>
+    <col min="9" max="9" width="12.1328125" customWidth="1"/>
+    <col min="10" max="10" width="19.86328125" customWidth="1"/>
+    <col min="11" max="11" width="12.46484375" customWidth="1"/>
+    <col min="12" max="12" width="79.53125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-    </row>
-    <row r="2" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+    </row>
+    <row r="2" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A2" s="12" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E2" s="12" t="s">
         <v>1</v>
@@ -1134,7 +1155,7 @@
         <v>4</v>
       </c>
       <c r="I2" s="12" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J2" s="12" t="s">
         <v>5</v>
@@ -1146,12 +1167,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1159,29 +1180,29 @@
       <c r="F3">
         <v>1</v>
       </c>
-      <c r="H3" s="2">
-        <v>8.7200000000000006</v>
+      <c r="H3" s="24">
+        <v>5.5</v>
       </c>
       <c r="I3" s="2">
         <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
-        <v>8.7200000000000006</v>
+        <v>5.5</v>
       </c>
       <c r="J3" t="s">
-        <v>10</v>
+        <v>92</v>
       </c>
       <c r="K3" t="s">
+        <v>67</v>
+      </c>
+      <c r="L3" s="14" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
         <v>11</v>
       </c>
-      <c r="L3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -1194,18 +1215,18 @@
         <v>0.5</v>
       </c>
       <c r="K4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A5" s="3">
         <v>555</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -1218,55 +1239,55 @@
         <v>0.68</v>
       </c>
       <c r="J5" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>97</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
       <c r="H6" s="2">
-        <v>0.11</v>
+        <v>0.42</v>
       </c>
       <c r="I6" s="2">
         <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
-        <v>0.11</v>
+        <v>0.42</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="K6" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="L6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E7" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F7">
         <v>3</v>
@@ -1279,24 +1300,24 @@
         <v>0.255</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C8" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E8" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -1309,24 +1330,24 @@
         <v>2.48</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F9">
         <v>2</v>
@@ -1338,15 +1359,15 @@
       </c>
       <c r="J9" s="4"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D10" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -1360,18 +1381,18 @@
       </c>
       <c r="J10" s="4"/>
       <c r="K10" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C11" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D11" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F11">
         <v>1</v>
@@ -1385,18 +1406,18 @@
       </c>
       <c r="J11" s="4"/>
       <c r="K11" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C12" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D12" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F12">
         <v>1</v>
@@ -1408,16 +1429,16 @@
       </c>
       <c r="J12" s="4"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C13" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F13">
         <v>4</v>
@@ -1430,24 +1451,24 @@
         <v>0.27200000000000002</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L13" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C14" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D14" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F14">
         <v>3</v>
@@ -1459,18 +1480,18 @@
       </c>
       <c r="J14" s="4"/>
       <c r="K14" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C15" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D15" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -1481,18 +1502,18 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C16" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D16" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -1506,18 +1527,18 @@
       </c>
       <c r="J16" s="4"/>
       <c r="K16" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C17" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D17" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F17">
         <v>2</v>
@@ -1531,18 +1552,18 @@
       </c>
       <c r="J17" s="4"/>
       <c r="K17" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C18" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D18" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F18">
         <v>1</v>
@@ -1556,18 +1577,18 @@
       </c>
       <c r="J18" s="4"/>
       <c r="K18" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C19" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F19">
         <v>2</v>
@@ -1581,15 +1602,15 @@
       </c>
       <c r="J19" s="4"/>
       <c r="K19" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C20" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D20" s="3"/>
       <c r="F20">
@@ -1603,18 +1624,18 @@
         <v>0.05</v>
       </c>
       <c r="K20" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C21" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F21">
         <v>4</v>
@@ -1627,12 +1648,12 @@
         <v>0.2</v>
       </c>
       <c r="K21" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F22">
         <v>2</v>
@@ -1646,15 +1667,15 @@
       </c>
       <c r="J22" s="4"/>
       <c r="K22" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="L22" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F23">
         <v>1</v>
@@ -1668,15 +1689,15 @@
       </c>
       <c r="J23" s="4"/>
       <c r="K23" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="L23" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -1690,15 +1711,15 @@
       </c>
       <c r="J24" s="4"/>
       <c r="K24" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="L24" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F25">
         <v>1</v>
@@ -1712,15 +1733,15 @@
       </c>
       <c r="J25" s="4"/>
       <c r="K25" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="L25" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F26">
         <v>1</v>
@@ -1734,18 +1755,18 @@
       </c>
       <c r="J26" s="4"/>
       <c r="K26" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="L26" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D27" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F27">
         <v>1</v>
@@ -1759,69 +1780,84 @@
       </c>
       <c r="J27" s="4"/>
       <c r="K27" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="L27" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
+        <v>90</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+      <c r="H28" s="2">
+        <v>1</v>
+      </c>
+      <c r="I28" s="2">
+        <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
+        <v>1</v>
+      </c>
+      <c r="J28" s="4"/>
+      <c r="K28" t="s">
         <v>94</v>
       </c>
-      <c r="F28">
-        <v>1</v>
-      </c>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2">
-        <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
-        <v>0</v>
-      </c>
-      <c r="J28" s="4"/>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D29" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F29">
         <v>1</v>
       </c>
-      <c r="H29" s="2"/>
+      <c r="H29" s="2">
+        <v>1.52</v>
+      </c>
       <c r="I29" s="2">
         <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="J29" s="4"/>
       <c r="K29" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+      <c r="L29" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F30">
         <v>2</v>
       </c>
-      <c r="H30" s="2"/>
+      <c r="H30" s="2">
+        <v>0.43</v>
+      </c>
       <c r="I30" s="2">
         <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="J30" s="4"/>
       <c r="K30" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+      <c r="L30" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D31" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F31">
         <v>2</v>
@@ -1835,15 +1871,15 @@
       </c>
       <c r="J31" s="4"/>
       <c r="K31" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D32" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F32">
         <v>2</v>
@@ -1857,76 +1893,76 @@
       </c>
       <c r="J32" s="4"/>
       <c r="K32" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.45">
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A34" s="6" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B34" s="6"/>
       <c r="C34" s="8">
         <v>46126</v>
       </c>
-      <c r="D34" s="15" t="e" vm="1">
+      <c r="D34" s="16" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="E34" s="16"/>
-      <c r="F34" s="17"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="18"/>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A35" s="7" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B35" s="7"/>
       <c r="C35" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D35" s="18"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="19"/>
+        <v>28</v>
+      </c>
+      <c r="D35" s="19"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="20"/>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A36" s="7" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B36" s="7"/>
       <c r="C36" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="D36" s="18"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="19"/>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+        <v>46</v>
+      </c>
+      <c r="D36" s="19"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="20"/>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A37" s="10" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B37" s="10"/>
       <c r="C37" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="D37" s="20"/>
-      <c r="E37" s="21"/>
-      <c r="F37" s="22"/>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+      <c r="D37" s="21"/>
+      <c r="E37" s="22"/>
+      <c r="F37" s="23"/>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
     </row>
@@ -1935,10 +1971,13 @@
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="D34:F37"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="L3" r:id="rId1" xr:uid="{B3065FAB-E838-4A51-A82F-630335C42D81}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
--- a/BOM_LignePassionIIm.xlsx
+++ b/BOM_LignePassionIIm.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7a43dc3239fed0de/PCB_Perso/PCB_IIm_Ligne/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="348" documentId="8_{D99A6803-265B-43E3-9609-960129D8CCE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8FC5694C-C4FF-4997-9199-556382D8D3CF}"/>
+  <xr:revisionPtr revIDLastSave="403" documentId="8_{D99A6803-265B-43E3-9609-960129D8CCE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8722E48D-2DF3-4A2A-B563-0D5FA706DD67}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{C3AD9156-7CE6-4A1E-A3FD-D08ECF380023}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="113">
   <si>
     <t>Quoi</t>
   </si>
@@ -294,18 +294,12 @@
     <t>3 pos 3 cont</t>
   </si>
   <si>
-    <t>J1, J2, (J3)</t>
-  </si>
-  <si>
     <t>R1, R2, R5, R6</t>
   </si>
   <si>
     <t>Pour led</t>
   </si>
   <si>
-    <t>R4</t>
-  </si>
-  <si>
     <t>R7</t>
   </si>
   <si>
@@ -318,15 +312,6 @@
     <t>270R 1/4W</t>
   </si>
   <si>
-    <t>Resistance (À changer)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">470R </t>
-  </si>
-  <si>
-    <t>R12, R15</t>
-  </si>
-  <si>
     <t>1K 1/4W</t>
   </si>
   <si>
@@ -355,14 +340,72 @@
   </si>
   <si>
     <t>https://www.conrad.ch/fr/p/infineon-technologies-irfu5305pbf-mosfet-1-canal-p-110-w-i-pak-162729.html?insert=UP</t>
+  </si>
+  <si>
+    <t>470R  1/4W</t>
+  </si>
+  <si>
+    <t>J1, J2, J4</t>
+  </si>
+  <si>
+    <t>Resistance de Shunt</t>
+  </si>
+  <si>
+    <t>https://de.aliexpress.com/item/1005004002774546.html?spm=a2g0o.productlist.main.6.18ab20bbmHcGED&amp;aem_p4p_detail=202608121236371154182288705600000113625&amp;algo_pvid=00e039e6-f960-4780-bcc3-bce9310ef85b&amp;pdp_ext_f=%7B%22order%22%3A%222407%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005004002774546%7C_p_origin_prod%3A&amp;search_p4p_id=202608121236371154182288705600000113625_10</t>
+  </si>
+  <si>
+    <t>R3</t>
+  </si>
+  <si>
+    <t>Diode Roue Libr Mosfet</t>
+  </si>
+  <si>
+    <t>MUR420G</t>
+  </si>
+  <si>
+    <t>https://www.digikey.ch/fr/products/detail/onsemi/MUR420G/1482828?s=N4IgTCBcDaILIFUBKAWMAGA4iAugXyA</t>
+  </si>
+  <si>
+    <t>Onsemi</t>
+  </si>
+  <si>
+    <t>D5</t>
+  </si>
+  <si>
+    <t>Dissipateur termique</t>
+  </si>
+  <si>
+    <t>https://de.aliexpress.com/item/32676786935.html?spm=a2g0o.productlist.main.10.79176c53yfCzKI&amp;algo_pvid=595eca82-0e86-47a6-9df1-3203eee67bde&amp;pdp_ext_f=%7B%22order%22%3A%22175%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A32676786935%7C_p_origin_prod%3A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For </t>
+  </si>
+  <si>
+    <t>Resistance Gate FET</t>
+  </si>
+  <si>
+    <t>R14</t>
+  </si>
+  <si>
+    <t>100R 5W</t>
+  </si>
+  <si>
+    <t>https://de.aliexpress.com/item/1005005674103930.html?spm=a2g0o.productlist.main.1.637ejuNajuNa2p&amp;algo_pvid=b22cab55-934f-49f0-ab1c-9d69b66ca252&amp;pdp_ext_f=%7B%22order%22%3A%223052%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005005674103930%7C_p_origin_prod%3A</t>
+  </si>
+  <si>
+    <t>1R 2W</t>
+  </si>
+  <si>
+    <t>R4, R12, R15</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;CHF&quot;_-;\-* #,##0.00\ &quot;CHF&quot;_-;_-* &quot;-&quot;??\ &quot;CHF&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;CHF&quot;"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -548,7 +591,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -609,7 +652,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Lien hypertexte" xfId="2" builtinId="8"/>
@@ -760,8 +804,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{69225E41-4DDD-470A-8E1A-242AA800D3ED}" name="Tableau2" displayName="Tableau2" ref="A2:L32" totalsRowShown="0" headerRowDxfId="4" headerRowBorderDxfId="3">
-  <autoFilter ref="A2:L32" xr:uid="{69225E41-4DDD-470A-8E1A-242AA800D3ED}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{69225E41-4DDD-470A-8E1A-242AA800D3ED}" name="Tableau2" displayName="Tableau2" ref="A2:L35" totalsRowShown="0" headerRowDxfId="4" headerRowBorderDxfId="3">
+  <autoFilter ref="A2:L35" xr:uid="{69225E41-4DDD-470A-8E1A-242AA800D3ED}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{4A89CEB1-B61F-4362-A305-55FE015108C9}" name="Quoi"/>
     <tableColumn id="12" xr3:uid="{DA7C8F96-35E1-4693-8B7A-073C30B6A014}" name="Variante"/>
@@ -1099,7 +1143,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3B7EC6F-57FE-4577-A1D4-89717E48955F}">
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:L43"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="25.53125" customWidth="1"/>
@@ -1180,7 +1224,7 @@
       <c r="F3">
         <v>1</v>
       </c>
-      <c r="H3" s="24">
+      <c r="H3" s="25">
         <v>5.5</v>
       </c>
       <c r="I3" s="2">
@@ -1188,13 +1232,13 @@
         <v>5.5</v>
       </c>
       <c r="J3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="K3" t="s">
         <v>67</v>
       </c>
       <c r="L3" s="14" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.45">
@@ -1256,7 +1300,7 @@
         <v>15</v>
       </c>
       <c r="E6" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -1275,7 +1319,7 @@
         <v>67</v>
       </c>
       <c r="L6" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.45">
@@ -1347,7 +1391,7 @@
         <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="F9">
         <v>2</v>
@@ -1431,56 +1475,63 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>53</v>
+        <v>99</v>
       </c>
       <c r="C13" t="s">
-        <v>54</v>
-      </c>
-      <c r="D13" s="5"/>
+        <v>103</v>
+      </c>
       <c r="E13" t="s">
-        <v>19</v>
+        <v>100</v>
       </c>
       <c r="F13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H13" s="2">
-        <v>6.8000000000000005E-2</v>
-      </c>
-      <c r="I13" s="2">
-        <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
-        <v>0.27200000000000002</v>
+        <v>0.50900000000000001</v>
+      </c>
+      <c r="I13" s="24">
+        <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
+        <v>0.50900000000000001</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>18</v>
+        <v>102</v>
       </c>
       <c r="K13" t="s">
         <v>10</v>
       </c>
       <c r="L13" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C14" t="s">
-        <v>78</v>
-      </c>
-      <c r="D14" t="s">
-        <v>57</v>
+        <v>54</v>
+      </c>
+      <c r="D14" s="5"/>
+      <c r="E14" t="s">
+        <v>19</v>
       </c>
       <c r="F14">
-        <v>3</v>
-      </c>
-      <c r="H14" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="H14" s="2">
+        <v>6.8000000000000005E-2</v>
+      </c>
       <c r="I14" s="2">
         <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
-        <v>0</v>
-      </c>
-      <c r="J14" s="4"/>
+        <v>0.27200000000000002</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="K14" t="s">
-        <v>55</v>
+        <v>10</v>
+      </c>
+      <c r="L14" s="14" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.45">
@@ -1488,46 +1539,44 @@
         <v>58</v>
       </c>
       <c r="C15" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
       <c r="D15" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2">
         <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
         <v>0</v>
       </c>
+      <c r="J15" s="4"/>
       <c r="K15" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="C16" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="D16" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="F16">
-        <v>5</v>
-      </c>
-      <c r="H16" s="2">
-        <v>0.05</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H16" s="2"/>
       <c r="I16" s="2">
         <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
-        <v>0.25</v>
-      </c>
-      <c r="J16" s="4"/>
+        <v>0</v>
+      </c>
       <c r="K16" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.45">
@@ -1535,20 +1584,20 @@
         <v>24</v>
       </c>
       <c r="C17" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D17" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="F17">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H17" s="2">
         <v>0.05</v>
       </c>
       <c r="I17" s="2">
         <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="J17" s="4"/>
       <c r="K17" t="s">
@@ -1560,20 +1609,20 @@
         <v>24</v>
       </c>
       <c r="C18" t="s">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="D18" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H18" s="2">
         <v>0.05</v>
       </c>
       <c r="I18" s="2">
         <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
-        <v>0.05</v>
+        <v>0.15000000000000002</v>
       </c>
       <c r="J18" s="4"/>
       <c r="K18" t="s">
@@ -1585,20 +1634,20 @@
         <v>24</v>
       </c>
       <c r="C19" t="s">
-        <v>83</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>85</v>
+        <v>80</v>
+      </c>
+      <c r="D19" t="s">
+        <v>94</v>
       </c>
       <c r="F19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H19" s="2">
         <v>0.05</v>
       </c>
       <c r="I19" s="2">
         <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="J19" s="4"/>
       <c r="K19" t="s">
@@ -1607,119 +1656,134 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>86</v>
+        <v>24</v>
       </c>
       <c r="C20" t="s">
         <v>81</v>
       </c>
-      <c r="D20" s="3"/>
+      <c r="D20" s="3" t="s">
+        <v>83</v>
+      </c>
       <c r="F20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" s="2">
         <v>0.05</v>
       </c>
       <c r="I20" s="2">
         <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
-        <v>0.05</v>
-      </c>
+        <v>0.1</v>
+      </c>
+      <c r="J20" s="4"/>
       <c r="K20" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>24</v>
+        <v>107</v>
       </c>
       <c r="C21" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="F21">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H21" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="I21" s="2">
-        <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
-        <v>0.2</v>
-      </c>
+        <v>0.15</v>
+      </c>
+      <c r="I21" s="24">
+        <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
+        <v>0.15</v>
+      </c>
+      <c r="J21" s="4"/>
       <c r="K21" t="s">
-        <v>23</v>
+        <v>55</v>
+      </c>
+      <c r="L21" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>59</v>
+        <v>96</v>
+      </c>
+      <c r="C22" t="s">
+        <v>98</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>111</v>
       </c>
       <c r="F22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H22" s="2">
-        <v>2.4500000000000002</v>
-      </c>
-      <c r="I22" s="2">
-        <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
-        <v>4.9000000000000004</v>
+        <v>0.08</v>
+      </c>
+      <c r="I22" s="24">
+        <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
+        <v>0.08</v>
       </c>
       <c r="J22" s="4"/>
       <c r="K22" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="L22" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>61</v>
+        <v>24</v>
+      </c>
+      <c r="C23" t="s">
+        <v>78</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>79</v>
       </c>
       <c r="F23">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H23" s="2">
-        <v>5.1999999999999998E-2</v>
+        <v>0.05</v>
       </c>
       <c r="I23" s="2">
         <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
-        <v>5.1999999999999998E-2</v>
-      </c>
-      <c r="J23" s="4"/>
+        <v>0.2</v>
+      </c>
       <c r="K23" t="s">
-        <v>55</v>
-      </c>
-      <c r="L23" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H24" s="2">
-        <v>5.1999999999999998E-2</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="I24" s="2">
         <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
-        <v>5.1999999999999998E-2</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="J24" s="4"/>
       <c r="K24" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="L24" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F25">
         <v>1</v>
@@ -1741,7 +1805,7 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F26">
         <v>1</v>
@@ -1763,221 +1827,291 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>60</v>
-      </c>
-      <c r="D27" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F27">
         <v>1</v>
       </c>
       <c r="H27" s="2">
-        <v>4.25</v>
+        <v>5.1999999999999998E-2</v>
       </c>
       <c r="I27" s="2">
         <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
-        <v>4.25</v>
+        <v>5.1999999999999998E-2</v>
       </c>
       <c r="J27" s="4"/>
       <c r="K27" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="L27" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="F28">
         <v>1</v>
       </c>
       <c r="H28" s="2">
-        <v>1</v>
+        <v>5.1999999999999998E-2</v>
       </c>
       <c r="I28" s="2">
         <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
-        <v>1</v>
+        <v>5.1999999999999998E-2</v>
       </c>
       <c r="J28" s="4"/>
       <c r="K28" t="s">
-        <v>94</v>
+        <v>55</v>
+      </c>
+      <c r="L28" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="D29" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="F29">
         <v>1</v>
       </c>
       <c r="H29" s="2">
-        <v>1.52</v>
+        <v>4.25</v>
       </c>
       <c r="I29" s="2">
         <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
-        <v>1.52</v>
+        <v>4.25</v>
       </c>
       <c r="J29" s="4"/>
       <c r="K29" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="L29" t="s">
-        <v>95</v>
+        <v>66</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="F30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H30" s="2">
-        <v>0.43</v>
+        <v>1</v>
       </c>
       <c r="I30" s="2">
         <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="J30" s="4"/>
       <c r="K30" t="s">
-        <v>55</v>
-      </c>
-      <c r="L30" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D31" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H31" s="2">
-        <v>0.05</v>
+        <v>1.52</v>
       </c>
       <c r="I31" s="2">
         <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
-        <v>0.1</v>
+        <v>1.52</v>
       </c>
       <c r="J31" s="4"/>
       <c r="K31" t="s">
         <v>55</v>
       </c>
+      <c r="L31" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>74</v>
-      </c>
-      <c r="D32" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F32">
         <v>2</v>
       </c>
       <c r="H32" s="2">
-        <v>0.05</v>
+        <v>0.43</v>
       </c>
       <c r="I32" s="2">
         <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
-        <v>0.1</v>
+        <v>0.86</v>
       </c>
       <c r="J32" s="4"/>
       <c r="K32" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A34" s="6" t="s">
+      <c r="L32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A33" t="s">
+        <v>74</v>
+      </c>
+      <c r="D33" t="s">
+        <v>75</v>
+      </c>
+      <c r="F33">
+        <v>2</v>
+      </c>
+      <c r="H33" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="I33" s="2">
+        <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
+        <v>0.1</v>
+      </c>
+      <c r="J33" s="4"/>
+      <c r="K33" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A34" t="s">
+        <v>74</v>
+      </c>
+      <c r="D34" t="s">
+        <v>76</v>
+      </c>
+      <c r="F34">
+        <v>2</v>
+      </c>
+      <c r="H34" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="I34" s="2">
+        <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
+        <v>0.1</v>
+      </c>
+      <c r="J34" s="4"/>
+      <c r="K34" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A35" t="s">
+        <v>104</v>
+      </c>
+      <c r="D35" t="s">
+        <v>106</v>
+      </c>
+      <c r="F35">
+        <v>1</v>
+      </c>
+      <c r="H35" s="2">
+        <v>0.15</v>
+      </c>
+      <c r="I35" s="24">
+        <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
+        <v>0.15</v>
+      </c>
+      <c r="J35" s="4"/>
+      <c r="K35" t="s">
+        <v>55</v>
+      </c>
+      <c r="L35" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A37" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B34" s="6"/>
-      <c r="C34" s="8">
+      <c r="B37" s="6"/>
+      <c r="C37" s="8">
         <v>46126</v>
       </c>
-      <c r="D34" s="16" t="e" vm="1">
+      <c r="D37" s="16" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="E34" s="17"/>
-      <c r="F34" s="18"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A35" s="7" t="s">
+      <c r="E37" s="17"/>
+      <c r="F37" s="18"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A38" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B35" s="7"/>
-      <c r="C35" s="9" t="s">
+      <c r="B38" s="7"/>
+      <c r="C38" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="D35" s="19"/>
-      <c r="E35" s="15"/>
-      <c r="F35" s="20"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A36" s="7" t="s">
+      <c r="D38" s="19"/>
+      <c r="E38" s="15"/>
+      <c r="F38" s="20"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A39" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B36" s="7"/>
-      <c r="C36" s="9" t="s">
+      <c r="B39" s="7"/>
+      <c r="C39" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="D36" s="19"/>
-      <c r="E36" s="15"/>
-      <c r="F36" s="20"/>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A37" s="10" t="s">
+      <c r="D39" s="19"/>
+      <c r="E39" s="15"/>
+      <c r="F39" s="20"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A40" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="B37" s="10"/>
-      <c r="C37" s="11" t="s">
+      <c r="B40" s="10"/>
+      <c r="C40" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D37" s="21"/>
-      <c r="E37" s="22"/>
-      <c r="F37" s="23"/>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A38" s="1"/>
-      <c r="B38" s="1"/>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A39" s="1"/>
-      <c r="B39" s="1"/>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A40" s="1"/>
-      <c r="B40" s="1"/>
+      <c r="D40" s="21"/>
+      <c r="E40" s="22"/>
+      <c r="F40" s="23"/>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A41" s="1"/>
+      <c r="B41" s="1"/>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A42" s="1"/>
+      <c r="B42" s="1"/>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A43" s="1"/>
+      <c r="B43" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:L1"/>
-    <mergeCell ref="D34:F37"/>
+    <mergeCell ref="D37:F40"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="L3" r:id="rId1" xr:uid="{B3065FAB-E838-4A51-A82F-630335C42D81}"/>
+    <hyperlink ref="L14" r:id="rId2" xr:uid="{2207D865-CE83-4458-802D-86175171E33D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
   </tableParts>
 </worksheet>
 </file>
--- a/BOM_LignePassionIIm.xlsx
+++ b/BOM_LignePassionIIm.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7a43dc3239fed0de/PCB_Perso/PCB_IIm_Ligne/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="403" documentId="8_{D99A6803-265B-43E3-9609-960129D8CCE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8722E48D-2DF3-4A2A-B563-0D5FA706DD67}"/>
+  <xr:revisionPtr revIDLastSave="404" documentId="8_{D99A6803-265B-43E3-9609-960129D8CCE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED07782D-FDD8-492C-B5DC-D6ED59226582}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{C3AD9156-7CE6-4A1E-A3FD-D08ECF380023}"/>
   </bookViews>
@@ -84,9 +84,6 @@
     <t xml:space="preserve">Lien </t>
   </si>
   <si>
-    <t>G2RK-2 DC12</t>
-  </si>
-  <si>
     <t>Relai BiStable de Puissance</t>
   </si>
   <si>
@@ -397,6 +394,9 @@
   </si>
   <si>
     <t>R4, R12, R15</t>
+  </si>
+  <si>
+    <t>41.52.6.012.4016</t>
   </si>
 </sst>
 </file>
@@ -405,7 +405,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;CHF&quot;_-;\-* #,##0.00\ &quot;CHF&quot;_-;_-* &quot;-&quot;??\ &quot;CHF&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;CHF&quot;"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;CHF&quot;"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -591,7 +591,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -625,6 +625,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -652,8 +653,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Lien hypertexte" xfId="2" builtinId="8"/>
@@ -1158,33 +1157,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A1" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
+      <c r="A1" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
     </row>
     <row r="2" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A2" s="12" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E2" s="12" t="s">
         <v>1</v>
@@ -1199,7 +1198,7 @@
         <v>4</v>
       </c>
       <c r="I2" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J2" s="12" t="s">
         <v>5</v>
@@ -1213,18 +1212,18 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>112</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
-      <c r="H3" s="25">
+      <c r="H3" s="15">
         <v>5.5</v>
       </c>
       <c r="I3" s="2">
@@ -1232,21 +1231,21 @@
         <v>5.5</v>
       </c>
       <c r="J3" t="s">
+        <v>86</v>
+      </c>
+      <c r="K3" t="s">
+        <v>66</v>
+      </c>
+      <c r="L3" s="14" t="s">
         <v>87</v>
-      </c>
-      <c r="K3" t="s">
-        <v>67</v>
-      </c>
-      <c r="L3" s="14" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -1259,7 +1258,7 @@
         <v>0.5</v>
       </c>
       <c r="K4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.45">
@@ -1267,10 +1266,10 @@
         <v>555</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -1283,24 +1282,24 @@
         <v>0.68</v>
       </c>
       <c r="J5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -1313,25 +1312,25 @@
         <v>0.42</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="L6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" t="s">
         <v>38</v>
-      </c>
-      <c r="E7" t="s">
-        <v>39</v>
       </c>
       <c r="F7">
         <v>3</v>
@@ -1344,24 +1343,24 @@
         <v>0.255</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E8" t="s">
         <v>41</v>
-      </c>
-      <c r="C8" t="s">
-        <v>71</v>
-      </c>
-      <c r="E8" t="s">
-        <v>42</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -1374,24 +1373,24 @@
         <v>2.48</v>
       </c>
       <c r="J8" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="K8" t="s">
+        <v>9</v>
+      </c>
+      <c r="L8" t="s">
         <v>43</v>
-      </c>
-      <c r="K8" t="s">
-        <v>10</v>
-      </c>
-      <c r="L8" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F9">
         <v>2</v>
@@ -1405,13 +1404,13 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" t="s">
         <v>47</v>
-      </c>
-      <c r="D10" t="s">
-        <v>48</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -1425,18 +1424,18 @@
       </c>
       <c r="J10" s="4"/>
       <c r="K10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C11" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" t="s">
         <v>49</v>
-      </c>
-      <c r="D11" t="s">
-        <v>50</v>
       </c>
       <c r="F11">
         <v>1</v>
@@ -1450,18 +1449,18 @@
       </c>
       <c r="J11" s="4"/>
       <c r="K11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C12" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" t="s">
         <v>51</v>
-      </c>
-      <c r="D12" t="s">
-        <v>52</v>
       </c>
       <c r="F12">
         <v>1</v>
@@ -1475,13 +1474,13 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
+        <v>98</v>
+      </c>
+      <c r="C13" t="s">
+        <v>102</v>
+      </c>
+      <c r="E13" t="s">
         <v>99</v>
-      </c>
-      <c r="C13" t="s">
-        <v>103</v>
-      </c>
-      <c r="E13" t="s">
-        <v>100</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -1489,30 +1488,30 @@
       <c r="H13" s="2">
         <v>0.50900000000000001</v>
       </c>
-      <c r="I13" s="24">
+      <c r="I13" s="2">
         <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
         <v>0.50900000000000001</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L13" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" t="s">
         <v>53</v>
-      </c>
-      <c r="C14" t="s">
-        <v>54</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F14">
         <v>4</v>
@@ -1525,24 +1524,24 @@
         <v>0.27200000000000002</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L14" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C15" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F15">
         <v>3</v>
@@ -1554,18 +1553,18 @@
       </c>
       <c r="J15" s="4"/>
       <c r="K15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -1576,18 +1575,18 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -1601,18 +1600,18 @@
       </c>
       <c r="J17" s="4"/>
       <c r="K17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C18" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F18">
         <v>3</v>
@@ -1626,18 +1625,18 @@
       </c>
       <c r="J18" s="4"/>
       <c r="K18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D19" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F19">
         <v>1</v>
@@ -1651,18 +1650,18 @@
       </c>
       <c r="J19" s="4"/>
       <c r="K19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F20">
         <v>2</v>
@@ -1676,18 +1675,18 @@
       </c>
       <c r="J20" s="4"/>
       <c r="K20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
+        <v>106</v>
+      </c>
+      <c r="C21" t="s">
         <v>107</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" s="3" t="s">
         <v>108</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>109</v>
       </c>
       <c r="F21">
         <v>1</v>
@@ -1695,27 +1694,27 @@
       <c r="H21" s="2">
         <v>0.15</v>
       </c>
-      <c r="I21" s="24">
+      <c r="I21" s="2">
         <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
         <v>0.15</v>
       </c>
       <c r="J21" s="4"/>
       <c r="K21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L21" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -1723,27 +1722,27 @@
       <c r="H22" s="2">
         <v>0.08</v>
       </c>
-      <c r="I22" s="24">
+      <c r="I22" s="2">
         <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
         <v>0.08</v>
       </c>
       <c r="J22" s="4"/>
       <c r="K22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L22" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C23" t="s">
+        <v>77</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>79</v>
       </c>
       <c r="F23">
         <v>4</v>
@@ -1756,12 +1755,12 @@
         <v>0.2</v>
       </c>
       <c r="K23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F24">
         <v>2</v>
@@ -1775,15 +1774,15 @@
       </c>
       <c r="J24" s="4"/>
       <c r="K24" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="L24" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F25">
         <v>1</v>
@@ -1797,15 +1796,15 @@
       </c>
       <c r="J25" s="4"/>
       <c r="K25" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L25" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F26">
         <v>1</v>
@@ -1819,15 +1818,15 @@
       </c>
       <c r="J26" s="4"/>
       <c r="K26" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L26" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F27">
         <v>1</v>
@@ -1841,15 +1840,15 @@
       </c>
       <c r="J27" s="4"/>
       <c r="K27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L27" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F28">
         <v>1</v>
@@ -1863,18 +1862,18 @@
       </c>
       <c r="J28" s="4"/>
       <c r="K28" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L28" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D29" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F29">
         <v>1</v>
@@ -1888,15 +1887,15 @@
       </c>
       <c r="J29" s="4"/>
       <c r="K29" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="L29" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F30">
         <v>1</v>
@@ -1910,15 +1909,15 @@
       </c>
       <c r="J30" s="4"/>
       <c r="K30" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D31" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F31">
         <v>1</v>
@@ -1932,15 +1931,15 @@
       </c>
       <c r="J31" s="4"/>
       <c r="K31" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L31" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F32">
         <v>2</v>
@@ -1954,18 +1953,18 @@
       </c>
       <c r="J32" s="4"/>
       <c r="K32" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L32" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
+        <v>73</v>
+      </c>
+      <c r="D33" t="s">
         <v>74</v>
-      </c>
-      <c r="D33" t="s">
-        <v>75</v>
       </c>
       <c r="F33">
         <v>2</v>
@@ -1979,15 +1978,15 @@
       </c>
       <c r="J33" s="4"/>
       <c r="K33" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D34" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F34">
         <v>2</v>
@@ -2001,15 +2000,15 @@
       </c>
       <c r="J34" s="4"/>
       <c r="K34" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D35" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F35">
         <v>1</v>
@@ -2017,16 +2016,16 @@
       <c r="H35" s="2">
         <v>0.15</v>
       </c>
-      <c r="I35" s="24">
+      <c r="I35" s="2">
         <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
         <v>0.15</v>
       </c>
       <c r="J35" s="4"/>
       <c r="K35" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L35" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.45">
@@ -2035,57 +2034,57 @@
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A37" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B37" s="6"/>
       <c r="C37" s="8">
         <v>46126</v>
       </c>
-      <c r="D37" s="16" t="e" vm="1">
+      <c r="D37" s="17" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="E37" s="17"/>
-      <c r="F37" s="18"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="19"/>
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A38" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B38" s="7"/>
       <c r="C38" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="D38" s="19"/>
-      <c r="E38" s="15"/>
-      <c r="F38" s="20"/>
+        <v>27</v>
+      </c>
+      <c r="D38" s="20"/>
+      <c r="E38" s="16"/>
+      <c r="F38" s="21"/>
       <c r="H38" s="2"/>
       <c r="I38" s="2"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A39" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B39" s="7"/>
       <c r="C39" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="D39" s="19"/>
-      <c r="E39" s="15"/>
-      <c r="F39" s="20"/>
+        <v>45</v>
+      </c>
+      <c r="D39" s="20"/>
+      <c r="E39" s="16"/>
+      <c r="F39" s="21"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A40" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B40" s="10"/>
       <c r="C40" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D40" s="21"/>
-      <c r="E40" s="22"/>
-      <c r="F40" s="23"/>
+        <v>32</v>
+      </c>
+      <c r="D40" s="22"/>
+      <c r="E40" s="23"/>
+      <c r="F40" s="24"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A41" s="1"/>

--- a/BOM_LignePassionIIm.xlsx
+++ b/BOM_LignePassionIIm.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7a43dc3239fed0de/PCB_Perso/PCB_IIm_Ligne/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="404" documentId="8_{D99A6803-265B-43E3-9609-960129D8CCE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED07782D-FDD8-492C-B5DC-D6ED59226582}"/>
+  <xr:revisionPtr revIDLastSave="416" documentId="8_{D99A6803-265B-43E3-9609-960129D8CCE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4FB48BB6-6415-4819-A75D-396767A58DF2}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{C3AD9156-7CE6-4A1E-A3FD-D08ECF380023}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="117">
   <si>
     <t>Quoi</t>
   </si>
@@ -397,6 +397,18 @@
   </si>
   <si>
     <t>41.52.6.012.4016</t>
+  </si>
+  <si>
+    <t>Diode Zener</t>
+  </si>
+  <si>
+    <t>D6</t>
+  </si>
+  <si>
+    <t>1N4733A</t>
+  </si>
+  <si>
+    <t>https://www.digikey.ch/fr/products/detail/onsemi/1n4733a/977210</t>
   </si>
 </sst>
 </file>
@@ -803,8 +815,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{69225E41-4DDD-470A-8E1A-242AA800D3ED}" name="Tableau2" displayName="Tableau2" ref="A2:L35" totalsRowShown="0" headerRowDxfId="4" headerRowBorderDxfId="3">
-  <autoFilter ref="A2:L35" xr:uid="{69225E41-4DDD-470A-8E1A-242AA800D3ED}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{69225E41-4DDD-470A-8E1A-242AA800D3ED}" name="Tableau2" displayName="Tableau2" ref="A2:L36" totalsRowShown="0" headerRowDxfId="4" headerRowBorderDxfId="3">
+  <autoFilter ref="A2:L36" xr:uid="{69225E41-4DDD-470A-8E1A-242AA800D3ED}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{4A89CEB1-B61F-4362-A305-55FE015108C9}" name="Quoi"/>
     <tableColumn id="12" xr3:uid="{DA7C8F96-35E1-4693-8B7A-073C30B6A014}" name="Variante"/>
@@ -1142,7 +1154,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3B7EC6F-57FE-4577-A1D4-89717E48955F}">
-  <dimension ref="A1:L43"/>
+  <dimension ref="A1:L44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="25.53125" customWidth="1"/>
@@ -2005,90 +2017,114 @@
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>103</v>
-      </c>
-      <c r="D35" t="s">
-        <v>105</v>
+        <v>113</v>
+      </c>
+      <c r="C35" t="s">
+        <v>114</v>
+      </c>
+      <c r="E35" t="s">
+        <v>115</v>
       </c>
       <c r="F35">
         <v>1</v>
       </c>
       <c r="H35" s="2">
-        <v>0.15</v>
+        <v>0.23</v>
       </c>
       <c r="I35" s="2">
         <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
-        <v>0.15</v>
+        <v>0.23</v>
       </c>
       <c r="J35" s="4"/>
       <c r="K35" t="s">
+        <v>9</v>
+      </c>
+      <c r="L35" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A36" t="s">
+        <v>103</v>
+      </c>
+      <c r="D36" t="s">
+        <v>105</v>
+      </c>
+      <c r="F36">
+        <v>1</v>
+      </c>
+      <c r="H36" s="2">
+        <v>0.15</v>
+      </c>
+      <c r="I36" s="2">
+        <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
+        <v>0.15</v>
+      </c>
+      <c r="J36" s="4"/>
+      <c r="K36" t="s">
         <v>54</v>
       </c>
-      <c r="L35" t="s">
+      <c r="L36" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="H36" s="2"/>
-      <c r="I36" s="2"/>
-    </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A37" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B37" s="6"/>
-      <c r="C37" s="8">
-        <v>46126</v>
-      </c>
-      <c r="D37" s="17" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
-      <c r="E37" s="18"/>
-      <c r="F37" s="19"/>
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A38" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B38" s="7"/>
-      <c r="C38" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D38" s="20"/>
-      <c r="E38" s="16"/>
-      <c r="F38" s="21"/>
+      <c r="A38" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B38" s="6"/>
+      <c r="C38" s="8">
+        <v>46126</v>
+      </c>
+      <c r="D38" s="17" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E38" s="18"/>
+      <c r="F38" s="19"/>
       <c r="H38" s="2"/>
       <c r="I38" s="2"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A39" s="7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B39" s="7"/>
       <c r="C39" s="9" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="D39" s="20"/>
       <c r="E39" s="16"/>
       <c r="F39" s="21"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A40" s="10" t="s">
+      <c r="A40" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B40" s="7"/>
+      <c r="C40" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D40" s="20"/>
+      <c r="E40" s="16"/>
+      <c r="F40" s="21"/>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A41" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B40" s="10"/>
-      <c r="C40" s="11" t="s">
+      <c r="B41" s="10"/>
+      <c r="C41" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="D40" s="22"/>
-      <c r="E40" s="23"/>
-      <c r="F40" s="24"/>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A41" s="1"/>
-      <c r="B41" s="1"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="23"/>
+      <c r="F41" s="24"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A42" s="1"/>
@@ -2098,10 +2134,14 @@
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
     </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1"/>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:L1"/>
-    <mergeCell ref="D37:F40"/>
+    <mergeCell ref="D38:F41"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="L3" r:id="rId1" xr:uid="{B3065FAB-E838-4A51-A82F-630335C42D81}"/>

--- a/BOM_LignePassionIIm.xlsx
+++ b/BOM_LignePassionIIm.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7a43dc3239fed0de/PCB_Perso/PCB_IIm_Ligne/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="416" documentId="8_{D99A6803-265B-43E3-9609-960129D8CCE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4FB48BB6-6415-4819-A75D-396767A58DF2}"/>
+  <xr:revisionPtr revIDLastSave="417" documentId="8_{D99A6803-265B-43E3-9609-960129D8CCE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{230BDB3F-DDE0-43F7-B1F7-44981D287893}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{C3AD9156-7CE6-4A1E-A3FD-D08ECF380023}"/>
   </bookViews>
@@ -1788,7 +1788,7 @@
       <c r="K24" t="s">
         <v>66</v>
       </c>
-      <c r="L24" t="s">
+      <c r="L24" s="14" t="s">
         <v>68</v>
       </c>
     </row>
@@ -2146,11 +2146,12 @@
   <hyperlinks>
     <hyperlink ref="L3" r:id="rId1" xr:uid="{B3065FAB-E838-4A51-A82F-630335C42D81}"/>
     <hyperlink ref="L14" r:id="rId2" xr:uid="{2207D865-CE83-4458-802D-86175171E33D}"/>
+    <hyperlink ref="L24" r:id="rId3" display="https://www.conrad.ch/de/p/tru-components-tc-13895648-rundsteckverbinder-stecker-buchsenkontakt-gesamtpolzahl-6-serie-rundsteckverbinder-gx16-3473912.html?insert=UP&amp;WT.srch=1&amp;ef_id=CjwKCAjw5s_QBhAdEiwADD_gBlB0NtPFlP1PxWWOBrmvbSo2JJn5T44wcE8r8-Hav4RDqu4GGAYJ1RoCRWEQAvD_BwE:G:s" xr:uid="{D4E7E61F-AE6E-48A3-9576-9A9FC4F56721}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
   <tableParts count="1">
-    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId5"/>
   </tableParts>
 </worksheet>
 </file>
--- a/BOM_LignePassionIIm.xlsx
+++ b/BOM_LignePassionIIm.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7a43dc3239fed0de/PCB_Perso/PCB_IIm_Ligne/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/79fc430203973324/TravauxMetriques/IIm/Passion IIm/PupitreLigne/AlimLigne_PassionIIm/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="417" documentId="8_{D99A6803-265B-43E3-9609-960129D8CCE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{230BDB3F-DDE0-43F7-B1F7-44981D287893}"/>
+  <xr:revisionPtr revIDLastSave="445" documentId="8_{D99A6803-265B-43E3-9609-960129D8CCE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0044CF36-3191-4FF6-82AC-6BD1CA97D11B}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{C3AD9156-7CE6-4A1E-A3FD-D08ECF380023}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{C3AD9156-7CE6-4A1E-A3FD-D08ECF380023}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="121">
   <si>
     <t>Quoi</t>
   </si>
@@ -409,6 +409,18 @@
   </si>
   <si>
     <t>https://www.digikey.ch/fr/products/detail/onsemi/1n4733a/977210</t>
+  </si>
+  <si>
+    <t>Toutes</t>
+  </si>
+  <si>
+    <t>2 Arduino 4 Autres</t>
+  </si>
+  <si>
+    <t>Etat</t>
+  </si>
+  <si>
+    <t>Commandé</t>
   </si>
 </sst>
 </file>
@@ -419,7 +431,7 @@
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;CHF&quot;_-;\-* #,##0.00\ &quot;CHF&quot;_-;_-* &quot;-&quot;??\ &quot;CHF&quot;_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;CHF&quot;"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -450,6 +462,13 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -603,7 +622,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -665,6 +684,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Lien hypertexte" xfId="2" builtinId="8"/>
@@ -815,9 +836,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{69225E41-4DDD-470A-8E1A-242AA800D3ED}" name="Tableau2" displayName="Tableau2" ref="A2:L36" totalsRowShown="0" headerRowDxfId="4" headerRowBorderDxfId="3">
-  <autoFilter ref="A2:L36" xr:uid="{69225E41-4DDD-470A-8E1A-242AA800D3ED}"/>
-  <tableColumns count="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{69225E41-4DDD-470A-8E1A-242AA800D3ED}" name="Tableau2" displayName="Tableau2" ref="A2:M36" totalsRowShown="0" headerRowDxfId="4" headerRowBorderDxfId="3">
+  <autoFilter ref="A2:M36" xr:uid="{69225E41-4DDD-470A-8E1A-242AA800D3ED}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:L36">
+    <sortCondition ref="K2:K36"/>
+  </sortState>
+  <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{4A89CEB1-B61F-4362-A305-55FE015108C9}" name="Quoi"/>
     <tableColumn id="12" xr3:uid="{DA7C8F96-35E1-4693-8B7A-073C30B6A014}" name="Variante"/>
     <tableColumn id="2" xr3:uid="{533B1CA6-1DE1-465B-9356-A9DA86FED988}" name="Ref PCB"/>
@@ -832,6 +856,7 @@
     <tableColumn id="9" xr3:uid="{B4254C8A-C5D7-4572-B86E-606DB6474104}" name="Fabriquant" dataDxfId="0"/>
     <tableColumn id="10" xr3:uid="{CF25DBB4-03E2-4519-889D-8135C83E9E6E}" name="Fournisseur "/>
     <tableColumn id="11" xr3:uid="{BD2CA350-D119-422A-BE3F-FA523F34F5B9}" name="Lien "/>
+    <tableColumn id="13" xr3:uid="{23078F5B-B4EF-4B8B-8C41-6B49DA287B4C}" name="Etat"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1154,21 +1179,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3B7EC6F-57FE-4577-A1D4-89717E48955F}">
-  <dimension ref="A1:L44"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:M44"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.53125" customWidth="1"/>
-    <col min="2" max="2" width="18.1328125" customWidth="1"/>
-    <col min="3" max="3" width="12.796875" customWidth="1"/>
-    <col min="4" max="4" width="14.1328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.86328125" customWidth="1"/>
-    <col min="9" max="9" width="12.1328125" customWidth="1"/>
-    <col min="10" max="10" width="19.86328125" customWidth="1"/>
-    <col min="11" max="11" width="12.46484375" customWidth="1"/>
-    <col min="12" max="12" width="79.53125" customWidth="1"/>
+    <col min="1" max="1" width="25.5546875" customWidth="1"/>
+    <col min="2" max="2" width="18.109375" customWidth="1"/>
+    <col min="3" max="3" width="12.77734375" customWidth="1"/>
+    <col min="4" max="4" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.88671875" customWidth="1"/>
+    <col min="9" max="9" width="12.109375" customWidth="1"/>
+    <col min="10" max="10" width="19.88671875" customWidth="1"/>
+    <col min="11" max="11" width="12.44140625" customWidth="1"/>
+    <col min="12" max="12" width="79.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
         <v>26</v>
       </c>
@@ -1184,7 +1209,7 @@
       <c r="K1" s="16"/>
       <c r="L1" s="16"/>
     </row>
-    <row r="2" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="12" t="s">
         <v>0</v>
       </c>
@@ -1221,762 +1246,817 @@
       <c r="L2" s="12" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M2" s="12" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>112</v>
+        <v>94</v>
+      </c>
+      <c r="D3" t="s">
+        <v>56</v>
       </c>
       <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="H3" s="15">
-        <v>5.5</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="H3" s="2"/>
       <c r="I3" s="2">
         <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
-        <v>5.5</v>
-      </c>
-      <c r="J3" t="s">
-        <v>86</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J3" s="4"/>
       <c r="K3" t="s">
-        <v>66</v>
-      </c>
-      <c r="L3" s="14" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>57</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>55</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
-      <c r="H4" s="2">
-        <v>0.5</v>
-      </c>
+      <c r="H4" s="2"/>
       <c r="I4" s="2">
         <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A5" s="3">
-        <v>555</v>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>106</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" t="s">
-        <v>34</v>
+        <v>107</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>108</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="H5" s="2">
-        <v>0.68</v>
+        <v>0.15</v>
       </c>
       <c r="I5" s="2">
         <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
-        <v>0.68</v>
-      </c>
-      <c r="J5" t="s">
-        <v>16</v>
-      </c>
+        <v>0.15</v>
+      </c>
+      <c r="J5" s="4"/>
       <c r="K5" t="s">
-        <v>9</v>
+        <v>54</v>
       </c>
       <c r="L5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" t="s">
-        <v>91</v>
+        <v>97</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>110</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
       <c r="H6" s="2">
-        <v>0.42</v>
+        <v>0.08</v>
       </c>
       <c r="I6" s="2">
         <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
-        <v>0.42</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>42</v>
-      </c>
+        <v>0.08</v>
+      </c>
+      <c r="J6" s="4"/>
       <c r="K6" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="L6" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" s="3"/>
-      <c r="C7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H7" s="2">
-        <v>8.5000000000000006E-2</v>
+        <v>5.1999999999999998E-2</v>
       </c>
       <c r="I7" s="2">
         <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
-        <v>0.255</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>17</v>
-      </c>
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="J7" s="4"/>
       <c r="K7" t="s">
-        <v>9</v>
+        <v>54</v>
       </c>
       <c r="L7" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" t="s">
-        <v>70</v>
-      </c>
-      <c r="E8" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="F8">
         <v>1</v>
       </c>
       <c r="H8" s="2">
-        <v>2.48</v>
+        <v>5.1999999999999998E-2</v>
       </c>
       <c r="I8" s="2">
         <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
-        <v>2.48</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>42</v>
-      </c>
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="J8" s="4"/>
       <c r="K8" t="s">
-        <v>9</v>
+        <v>54</v>
       </c>
       <c r="L8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D9" t="s">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="F9">
-        <v>2</v>
-      </c>
-      <c r="H9" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="H9" s="2">
+        <v>5.1999999999999998E-2</v>
+      </c>
       <c r="I9" s="2">
         <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
-        <v>0</v>
+        <v>5.1999999999999998E-2</v>
       </c>
       <c r="J9" s="4"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="K9" t="s">
+        <v>54</v>
+      </c>
+      <c r="L9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" t="s">
-        <v>46</v>
-      </c>
-      <c r="D10" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="F10">
         <v>1</v>
       </c>
       <c r="H10" s="2">
-        <v>0.05</v>
+        <v>5.1999999999999998E-2</v>
       </c>
       <c r="I10" s="2">
         <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
-        <v>0.05</v>
+        <v>5.1999999999999998E-2</v>
       </c>
       <c r="J10" s="4"/>
       <c r="K10" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
+        <v>54</v>
+      </c>
+      <c r="L10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="D11" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="F11">
         <v>1</v>
       </c>
       <c r="H11" s="2">
-        <v>0.05</v>
+        <v>1.52</v>
       </c>
       <c r="I11" s="2">
         <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
-        <v>0.05</v>
+        <v>1.52</v>
       </c>
       <c r="J11" s="4"/>
       <c r="K11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
+        <v>54</v>
+      </c>
+      <c r="L11" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" t="s">
-        <v>50</v>
-      </c>
-      <c r="D12" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="F12">
-        <v>1</v>
-      </c>
-      <c r="H12" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="H12" s="2">
+        <v>0.43</v>
+      </c>
       <c r="I12" s="2">
         <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="J12" s="4"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="K12" t="s">
+        <v>54</v>
+      </c>
+      <c r="L12" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>98</v>
-      </c>
-      <c r="C13" t="s">
-        <v>102</v>
-      </c>
-      <c r="E13" t="s">
-        <v>99</v>
+        <v>73</v>
+      </c>
+      <c r="D13" t="s">
+        <v>74</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H13" s="2">
-        <v>0.50900000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="I13" s="2">
         <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
-        <v>0.50900000000000001</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>101</v>
-      </c>
+        <v>0.1</v>
+      </c>
+      <c r="J13" s="4"/>
       <c r="K13" t="s">
-        <v>9</v>
-      </c>
-      <c r="L13" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>52</v>
-      </c>
-      <c r="C14" t="s">
-        <v>53</v>
-      </c>
-      <c r="D14" s="5"/>
-      <c r="E14" t="s">
-        <v>18</v>
+        <v>73</v>
+      </c>
+      <c r="D14" t="s">
+        <v>75</v>
       </c>
       <c r="F14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H14" s="2">
-        <v>6.8000000000000005E-2</v>
+        <v>0.05</v>
       </c>
       <c r="I14" s="2">
         <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
-        <v>0.27200000000000002</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>17</v>
-      </c>
+        <v>0.1</v>
+      </c>
+      <c r="J14" s="4"/>
       <c r="K14" t="s">
-        <v>9</v>
-      </c>
-      <c r="L14" s="14" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>57</v>
-      </c>
-      <c r="C15" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="D15" t="s">
-        <v>56</v>
+        <v>105</v>
       </c>
       <c r="F15">
-        <v>3</v>
-      </c>
-      <c r="H15" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="H15" s="2">
+        <v>0.15</v>
+      </c>
       <c r="I15" s="2">
         <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="J15" s="4"/>
       <c r="K15" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="L15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>57</v>
+        <v>8</v>
+      </c>
+      <c r="B16" t="s">
+        <v>117</v>
       </c>
       <c r="C16" t="s">
-        <v>24</v>
-      </c>
-      <c r="D16" t="s">
-        <v>55</v>
+        <v>12</v>
+      </c>
+      <c r="E16" t="s">
+        <v>112</v>
       </c>
       <c r="F16">
         <v>1</v>
       </c>
-      <c r="H16" s="2"/>
+      <c r="H16" s="15">
+        <v>5.5</v>
+      </c>
       <c r="I16" s="2">
         <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
-        <v>0</v>
+        <v>5.5</v>
+      </c>
+      <c r="J16" t="s">
+        <v>86</v>
       </c>
       <c r="K16" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.45">
+        <v>66</v>
+      </c>
+      <c r="L16" s="14" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>81</v>
-      </c>
-      <c r="D17" t="s">
-        <v>69</v>
+        <v>14</v>
+      </c>
+      <c r="E17" t="s">
+        <v>91</v>
       </c>
       <c r="F17">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H17" s="2">
-        <v>0.05</v>
+        <v>0.42</v>
       </c>
       <c r="I17" s="2">
         <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
-        <v>0.25</v>
-      </c>
-      <c r="J17" s="4"/>
+        <v>0.42</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>42</v>
+      </c>
       <c r="K17" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.45">
+        <v>66</v>
+      </c>
+      <c r="L17" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" t="s">
-        <v>111</v>
-      </c>
-      <c r="D18" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="F18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H18" s="2">
-        <v>0.05</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="I18" s="2">
         <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
-        <v>0.15000000000000002</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="J18" s="4"/>
       <c r="K18" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.45">
+        <v>66</v>
+      </c>
+      <c r="L18" s="14" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C19" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="D19" t="s">
-        <v>93</v>
+        <v>67</v>
       </c>
       <c r="F19">
         <v>1</v>
       </c>
       <c r="H19" s="2">
-        <v>0.05</v>
+        <v>4.25</v>
       </c>
       <c r="I19" s="2">
         <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
-        <v>0.05</v>
+        <v>4.25</v>
       </c>
       <c r="J19" s="4"/>
       <c r="K19" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A20" t="s">
-        <v>23</v>
+        <v>66</v>
+      </c>
+      <c r="L19" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A20" s="3">
+        <v>555</v>
+      </c>
+      <c r="B20" t="s">
+        <v>117</v>
       </c>
       <c r="C20" t="s">
-        <v>80</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="F20">
-        <v>2</v>
+        <v>15</v>
+      </c>
+      <c r="E20" t="s">
+        <v>34</v>
+      </c>
+      <c r="F20" s="25">
+        <v>1</v>
       </c>
       <c r="H20" s="2">
-        <v>0.05</v>
+        <v>0.68</v>
       </c>
       <c r="I20" s="2">
         <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
-        <v>0.1</v>
-      </c>
-      <c r="J20" s="4"/>
+        <v>0.68</v>
+      </c>
+      <c r="J20" t="s">
+        <v>16</v>
+      </c>
       <c r="K20" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+      <c r="L20" t="s">
+        <v>35</v>
+      </c>
+      <c r="M20" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>106</v>
+        <v>36</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>117</v>
       </c>
       <c r="C21" t="s">
-        <v>107</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="F21">
-        <v>1</v>
+        <v>37</v>
+      </c>
+      <c r="E21" t="s">
+        <v>38</v>
+      </c>
+      <c r="F21" s="25">
+        <v>3</v>
       </c>
       <c r="H21" s="2">
-        <v>0.15</v>
+        <v>8.5000000000000006E-2</v>
       </c>
       <c r="I21" s="2">
         <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
-        <v>0.15</v>
-      </c>
-      <c r="J21" s="4"/>
+        <v>0.255</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="K21" t="s">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="L21" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+      <c r="M21" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>95</v>
+        <v>40</v>
+      </c>
+      <c r="B22" t="s">
+        <v>117</v>
       </c>
       <c r="C22" t="s">
-        <v>97</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="F22">
+        <v>70</v>
+      </c>
+      <c r="E22" t="s">
+        <v>41</v>
+      </c>
+      <c r="F22" s="25">
         <v>1</v>
       </c>
       <c r="H22" s="2">
-        <v>0.08</v>
+        <v>2.48</v>
       </c>
       <c r="I22" s="2">
         <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
-        <v>0.08</v>
-      </c>
-      <c r="J22" s="4"/>
+        <v>2.48</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>42</v>
+      </c>
       <c r="K22" t="s">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="L22" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.45">
+        <v>43</v>
+      </c>
+      <c r="M22" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>98</v>
+      </c>
+      <c r="B23" t="s">
+        <v>117</v>
       </c>
       <c r="C23" t="s">
-        <v>77</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="F23">
+        <v>102</v>
+      </c>
+      <c r="E23" t="s">
+        <v>99</v>
+      </c>
+      <c r="F23" s="25">
+        <v>1</v>
+      </c>
+      <c r="H23" s="2">
+        <v>0.50900000000000001</v>
+      </c>
+      <c r="I23" s="2">
+        <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
+        <v>0.50900000000000001</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="K23" t="s">
+        <v>9</v>
+      </c>
+      <c r="L23" t="s">
+        <v>100</v>
+      </c>
+      <c r="M23" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>52</v>
+      </c>
+      <c r="B24" t="s">
+        <v>118</v>
+      </c>
+      <c r="C24" t="s">
+        <v>53</v>
+      </c>
+      <c r="D24" s="5"/>
+      <c r="E24" t="s">
+        <v>18</v>
+      </c>
+      <c r="F24" s="25">
         <v>4</v>
       </c>
-      <c r="H23" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="I23" s="2">
-        <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
-        <v>0.2</v>
-      </c>
-      <c r="K23" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A24" t="s">
-        <v>58</v>
-      </c>
-      <c r="F24">
-        <v>2</v>
-      </c>
       <c r="H24" s="2">
-        <v>2.4500000000000002</v>
+        <v>6.8000000000000005E-2</v>
       </c>
       <c r="I24" s="2">
         <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="J24" s="4"/>
+        <v>0.27200000000000002</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="K24" t="s">
-        <v>66</v>
+        <v>9</v>
       </c>
       <c r="L24" s="14" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+      <c r="M24" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>60</v>
-      </c>
-      <c r="F25">
+        <v>113</v>
+      </c>
+      <c r="B25" t="s">
+        <v>117</v>
+      </c>
+      <c r="C25" t="s">
+        <v>114</v>
+      </c>
+      <c r="E25" t="s">
+        <v>115</v>
+      </c>
+      <c r="F25" s="25">
         <v>1</v>
       </c>
       <c r="H25" s="2">
-        <v>5.1999999999999998E-2</v>
+        <v>0.23</v>
       </c>
       <c r="I25" s="2">
         <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
-        <v>5.1999999999999998E-2</v>
+        <v>0.23</v>
       </c>
       <c r="J25" s="4"/>
       <c r="K25" t="s">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="L25" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.45">
+        <v>116</v>
+      </c>
+      <c r="M25" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="F26">
         <v>1</v>
       </c>
       <c r="H26" s="2">
-        <v>5.1999999999999998E-2</v>
+        <v>1</v>
       </c>
       <c r="I26" s="2">
         <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
-        <v>5.1999999999999998E-2</v>
+        <v>1</v>
       </c>
       <c r="J26" s="4"/>
       <c r="K26" t="s">
-        <v>54</v>
-      </c>
-      <c r="L26" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.45">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>63</v>
+        <v>10</v>
+      </c>
+      <c r="B27" t="s">
+        <v>117</v>
+      </c>
+      <c r="C27" t="s">
+        <v>13</v>
       </c>
       <c r="F27">
         <v>1</v>
       </c>
       <c r="H27" s="2">
-        <v>5.1999999999999998E-2</v>
+        <v>0.5</v>
       </c>
       <c r="I27" s="2">
         <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
-        <v>5.1999999999999998E-2</v>
-      </c>
-      <c r="J27" s="4"/>
+        <v>0.5</v>
+      </c>
       <c r="K27" t="s">
-        <v>54</v>
-      </c>
-      <c r="L27" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.45">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>62</v>
+        <v>20</v>
+      </c>
+      <c r="C28" t="s">
+        <v>46</v>
+      </c>
+      <c r="D28" t="s">
+        <v>47</v>
       </c>
       <c r="F28">
         <v>1</v>
       </c>
       <c r="H28" s="2">
-        <v>5.1999999999999998E-2</v>
+        <v>0.05</v>
       </c>
       <c r="I28" s="2">
         <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
-        <v>5.1999999999999998E-2</v>
+        <v>0.05</v>
       </c>
       <c r="J28" s="4"/>
       <c r="K28" t="s">
-        <v>54</v>
-      </c>
-      <c r="L28" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.45">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>59</v>
+        <v>20</v>
+      </c>
+      <c r="C29" t="s">
+        <v>48</v>
       </c>
       <c r="D29" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="F29">
         <v>1</v>
       </c>
       <c r="H29" s="2">
-        <v>4.25</v>
+        <v>0.05</v>
       </c>
       <c r="I29" s="2">
         <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
-        <v>4.25</v>
+        <v>0.05</v>
       </c>
       <c r="J29" s="4"/>
       <c r="K29" t="s">
-        <v>66</v>
-      </c>
-      <c r="L29" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.45">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>84</v>
+        <v>23</v>
+      </c>
+      <c r="C30" t="s">
+        <v>81</v>
+      </c>
+      <c r="D30" t="s">
+        <v>69</v>
       </c>
       <c r="F30">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H30" s="2">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="I30" s="2">
         <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="J30" s="4"/>
       <c r="K30" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.45">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>71</v>
+        <v>23</v>
+      </c>
+      <c r="C31" t="s">
+        <v>111</v>
       </c>
       <c r="D31" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="F31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H31" s="2">
-        <v>1.52</v>
+        <v>0.05</v>
       </c>
       <c r="I31" s="2">
         <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
-        <v>1.52</v>
+        <v>0.15000000000000002</v>
       </c>
       <c r="J31" s="4"/>
       <c r="K31" t="s">
-        <v>54</v>
-      </c>
-      <c r="L31" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.45">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>72</v>
+        <v>23</v>
+      </c>
+      <c r="C32" t="s">
+        <v>79</v>
+      </c>
+      <c r="D32" t="s">
+        <v>93</v>
       </c>
       <c r="F32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H32" s="2">
-        <v>0.43</v>
+        <v>0.05</v>
       </c>
       <c r="I32" s="2">
         <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
-        <v>0.86</v>
+        <v>0.05</v>
       </c>
       <c r="J32" s="4"/>
       <c r="K32" t="s">
-        <v>54</v>
-      </c>
-      <c r="L32" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.45">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>73</v>
-      </c>
-      <c r="D33" t="s">
-        <v>74</v>
+        <v>23</v>
+      </c>
+      <c r="C33" t="s">
+        <v>80</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>82</v>
       </c>
       <c r="F33">
         <v>2</v>
@@ -1990,89 +2070,78 @@
       </c>
       <c r="J33" s="4"/>
       <c r="K33" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.45">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>73</v>
-      </c>
-      <c r="D34" t="s">
-        <v>75</v>
+        <v>23</v>
+      </c>
+      <c r="C34" t="s">
+        <v>77</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>78</v>
       </c>
       <c r="F34">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H34" s="2">
         <v>0.05</v>
       </c>
       <c r="I34" s="2">
         <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
-        <v>0.1</v>
-      </c>
-      <c r="J34" s="4"/>
+        <v>0.2</v>
+      </c>
       <c r="K34" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.45">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>113</v>
+        <v>20</v>
       </c>
       <c r="C35" t="s">
-        <v>114</v>
-      </c>
-      <c r="E35" t="s">
-        <v>115</v>
+        <v>44</v>
+      </c>
+      <c r="D35" t="s">
+        <v>85</v>
       </c>
       <c r="F35">
-        <v>1</v>
-      </c>
-      <c r="H35" s="2">
-        <v>0.23</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H35" s="2"/>
       <c r="I35" s="2">
         <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="J35" s="4"/>
-      <c r="K35" t="s">
-        <v>9</v>
-      </c>
-      <c r="L35" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.45">
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>103</v>
+        <v>20</v>
+      </c>
+      <c r="C36" t="s">
+        <v>50</v>
       </c>
       <c r="D36" t="s">
-        <v>105</v>
+        <v>51</v>
       </c>
       <c r="F36">
         <v>1</v>
       </c>
-      <c r="H36" s="2">
-        <v>0.15</v>
-      </c>
+      <c r="H36" s="2"/>
       <c r="I36" s="2">
         <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="J36" s="4"/>
-      <c r="K36" t="s">
-        <v>54</v>
-      </c>
-      <c r="L36" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.45">
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
         <v>29</v>
       </c>
@@ -2087,8 +2156,9 @@
       <c r="F38" s="19"/>
       <c r="H38" s="2"/>
       <c r="I38" s="2"/>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="J38" s="26"/>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="7" t="s">
         <v>28</v>
       </c>
@@ -2102,7 +2172,7 @@
       <c r="H39" s="2"/>
       <c r="I39" s="2"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
         <v>30</v>
       </c>
@@ -2114,7 +2184,7 @@
       <c r="E40" s="16"/>
       <c r="F40" s="21"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" s="10" t="s">
         <v>31</v>
       </c>
@@ -2126,15 +2196,15 @@
       <c r="E41" s="23"/>
       <c r="F41" s="24"/>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
     </row>
@@ -2144,9 +2214,9 @@
     <mergeCell ref="D38:F41"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="L3" r:id="rId1" xr:uid="{B3065FAB-E838-4A51-A82F-630335C42D81}"/>
-    <hyperlink ref="L14" r:id="rId2" xr:uid="{2207D865-CE83-4458-802D-86175171E33D}"/>
-    <hyperlink ref="L24" r:id="rId3" display="https://www.conrad.ch/de/p/tru-components-tc-13895648-rundsteckverbinder-stecker-buchsenkontakt-gesamtpolzahl-6-serie-rundsteckverbinder-gx16-3473912.html?insert=UP&amp;WT.srch=1&amp;ef_id=CjwKCAjw5s_QBhAdEiwADD_gBlB0NtPFlP1PxWWOBrmvbSo2JJn5T44wcE8r8-Hav4RDqu4GGAYJ1RoCRWEQAvD_BwE:G:s" xr:uid="{D4E7E61F-AE6E-48A3-9576-9A9FC4F56721}"/>
+    <hyperlink ref="L16" r:id="rId1" xr:uid="{B3065FAB-E838-4A51-A82F-630335C42D81}"/>
+    <hyperlink ref="L24" r:id="rId2" xr:uid="{2207D865-CE83-4458-802D-86175171E33D}"/>
+    <hyperlink ref="L18" r:id="rId3" display="https://www.conrad.ch/de/p/tru-components-tc-13895648-rundsteckverbinder-stecker-buchsenkontakt-gesamtpolzahl-6-serie-rundsteckverbinder-gx16-3473912.html?insert=UP&amp;WT.srch=1&amp;ef_id=CjwKCAjw5s_QBhAdEiwADD_gBlB0NtPFlP1PxWWOBrmvbSo2JJn5T44wcE8r8-Hav4RDqu4GGAYJ1RoCRWEQAvD_BwE:G:s" xr:uid="{D4E7E61F-AE6E-48A3-9576-9A9FC4F56721}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>

--- a/BOM_LignePassionIIm.xlsx
+++ b/BOM_LignePassionIIm.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7a43dc3239fed0de/PCB_Perso/PCB_IIm_Ligne/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="417" documentId="8_{D99A6803-265B-43E3-9609-960129D8CCE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{230BDB3F-DDE0-43F7-B1F7-44981D287893}"/>
+  <xr:revisionPtr revIDLastSave="418" documentId="8_{D99A6803-265B-43E3-9609-960129D8CCE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{457889A2-2181-4222-B105-155E598B04D9}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{C3AD9156-7CE6-4A1E-A3FD-D08ECF380023}"/>
   </bookViews>
@@ -1901,7 +1901,7 @@
       <c r="K29" t="s">
         <v>66</v>
       </c>
-      <c r="L29" t="s">
+      <c r="L29" s="14" t="s">
         <v>65</v>
       </c>
     </row>
@@ -2147,11 +2147,12 @@
     <hyperlink ref="L3" r:id="rId1" xr:uid="{B3065FAB-E838-4A51-A82F-630335C42D81}"/>
     <hyperlink ref="L14" r:id="rId2" xr:uid="{2207D865-CE83-4458-802D-86175171E33D}"/>
     <hyperlink ref="L24" r:id="rId3" display="https://www.conrad.ch/de/p/tru-components-tc-13895648-rundsteckverbinder-stecker-buchsenkontakt-gesamtpolzahl-6-serie-rundsteckverbinder-gx16-3473912.html?insert=UP&amp;WT.srch=1&amp;ef_id=CjwKCAjw5s_QBhAdEiwADD_gBlB0NtPFlP1PxWWOBrmvbSo2JJn5T44wcE8r8-Hav4RDqu4GGAYJ1RoCRWEQAvD_BwE:G:s" xr:uid="{D4E7E61F-AE6E-48A3-9576-9A9FC4F56721}"/>
+    <hyperlink ref="L29" r:id="rId4" xr:uid="{80488A4C-272B-449D-995C-AA3B3AC7AC6F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>
   <tableParts count="1">
-    <tablePart r:id="rId5"/>
+    <tablePart r:id="rId6"/>
   </tableParts>
 </worksheet>
 </file>